--- a/templates/deliverable/example/09_연계데이터목록정의서.xlsx
+++ b/templates/deliverable/example/09_연계데이터목록정의서.xlsx
@@ -12,39 +12,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>연계데이터 목록 정의서</t>
   </si>
   <si>
+    <t>연계정보 구분</t>
+  </si>
+  <si>
+    <t>연계 정보명</t>
+  </si>
+  <si>
+    <t>연계 주기</t>
+  </si>
+  <si>
+    <t>연계 항목명</t>
+  </si>
+  <si>
+    <t>연계 항목 설명</t>
+  </si>
+  <si>
+    <t>데이터 타입</t>
+  </si>
+  <si>
+    <t>데이터 길이</t>
+  </si>
+  <si>
+    <t>출처 DB명</t>
+  </si>
+  <si>
+    <t>출처 테이블명</t>
+  </si>
+  <si>
+    <t>출처 컬럼명</t>
+  </si>
+  <si>
+    <t>제공기관</t>
+  </si>
+  <si>
+    <t>활용기관</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
     <t>순번</t>
   </si>
   <si>
-    <t>송/수신</t>
-  </si>
-  <si>
-    <t>연계정보명</t>
-  </si>
-  <si>
-    <t>주기</t>
-  </si>
-  <si>
     <t>방식</t>
   </si>
   <si>
-    <t>연계항목</t>
-  </si>
-  <si>
-    <t>제공기관·시스템명</t>
-  </si>
-  <si>
-    <t>활용기관·시스템명</t>
-  </si>
-  <si>
     <t>연계기간</t>
-  </si>
-  <si>
-    <t>비고</t>
   </si>
 </sst>
 </file>
@@ -62,12 +80,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <b val="true"/>
     </font>
   </fonts>
@@ -121,8 +139,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
@@ -130,19 +148,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.0" customWidth="true"/>
-    <col min="2" max="2" width="12.0" customWidth="true"/>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="2" max="2" width="16.0" customWidth="true"/>
     <col min="3" max="3" width="14.0" customWidth="true"/>
-    <col min="4" max="4" width="8.0" customWidth="true"/>
-    <col min="5" max="5" width="8.0" customWidth="true"/>
-    <col min="6" max="6" width="12.0" customWidth="true"/>
-    <col min="7" max="7" width="22.0" customWidth="true"/>
-    <col min="8" max="8" width="22.0" customWidth="true"/>
-    <col min="9" max="9" width="12.0" customWidth="true"/>
-    <col min="10" max="10" width="8.0" customWidth="true"/>
+    <col min="4" max="4" width="16.0" customWidth="true"/>
+    <col min="5" max="5" width="20.0" customWidth="true"/>
+    <col min="6" max="6" width="16.0" customWidth="true"/>
+    <col min="7" max="7" width="16.0" customWidth="true"/>
+    <col min="8" max="8" width="16.0" customWidth="true"/>
+    <col min="9" max="9" width="18.0" customWidth="true"/>
+    <col min="10" max="10" width="16.0" customWidth="true"/>
+    <col min="11" max="11" width="12.0" customWidth="true"/>
+    <col min="12" max="12" width="12.0" customWidth="true"/>
+    <col min="13" max="13" width="8.0" customWidth="true"/>
+    <col min="14" max="14" width="8.0" customWidth="true"/>
+    <col min="15" max="15" width="8.0" customWidth="true"/>
+    <col min="16" max="16" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -180,6 +204,24 @@
       </c>
       <c r="J2" t="s" s="2">
         <v>10</v>
+      </c>
+      <c r="K2" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="O2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="P2" t="s" s="2">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -193,6 +235,12 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
